--- a/Neo_Phoenix/reports/daily_check.xlsx
+++ b/Neo_Phoenix/reports/daily_check.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="DaySummary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Game1_01_大分－宮崎" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game1_01_山口大学－広島大学" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game2_02_鳥取大学－下関市立大" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'DaySummary'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_大分－宮崎'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_山口大学－広島大学'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Game2_02_鳥取大学－下関市立大'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -544,7 +546,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20 20:32:28</t>
+          <t>2026-07-22 10:36:41</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -588,7 +590,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>1試合</t>
+          <t>2試合</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -598,7 +600,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>8件</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -663,17 +665,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>□ 01_大分－宮崎</t>
+          <t>□ 01_山口大学－広島大学</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>4回表 1点目　非自責</t>
+          <t>3回裏 2点目　非自責</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -687,17 +689,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>□ 01_大分－宮崎</t>
+          <t>□ 01_山口大学－広島大学</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>5回裏 4点目　非自責</t>
+          <t>3回裏 3点目　非自責</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -711,12 +713,12 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>□ 01_大分－宮崎</t>
+          <t>□ 02_鳥取大学－下関市立大</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>5回裏 6点目　非自責</t>
+          <t>2回表 2点目　非自責</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -735,17 +737,17 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>□ 01_大分－宮崎</t>
+          <t>□ 02_鳥取大学－下関市立大</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>6回裏 1点目　非自責</t>
+          <t>3回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>失策出塁</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -755,6 +757,102 @@
       </c>
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥取大学－下関市立大</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>5回表 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥取大学－下関市立大</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>7回表 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥取大学－下関市立大</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>7回表 2点目　非自責</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>捕逸生還</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥取大学－下関市立大</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>7回表 3点目　非自責</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -772,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -798,7 +896,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>01_大分－宮崎：EasyScore補正票</t>
+          <t>01_山口大学－広島大学：EasyScore補正票</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -823,7 +921,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>01_大分－宮崎</t>
+          <t>01_山口大学－広島大学</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -846,7 +944,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -854,7 +952,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -862,7 +960,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -941,7 +1039,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>4回表 1点目</t>
+          <t>3回裏 2点目</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -951,12 +1049,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>西原 凜</t>
+          <t>新村 勇翔</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -973,7 +1071,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5回裏 4点目</t>
+          <t>3回裏 3点目</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -983,12 +1081,12 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>杉 ケニス 千音々</t>
+          <t>橋本 涼</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -998,124 +1096,92 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>5回裏 6点目</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Virtual生還不能</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>太田 直哉</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A11" s="1" t="inlineStr"/>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr"/>
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1" t="inlineStr"/>
+      <c r="F11" s="1" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>6回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>失策出塁</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>窪田 翔太</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="1" t="inlineStr"/>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>徳竹 智大</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="D13" s="1" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>投手サマリー</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>伊敷 聖羅</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>失点</t>
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>志賀 亮佑</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1" t="inlineStr"/>
       <c r="E16" s="1" t="inlineStr"/>
@@ -1123,9 +1189,9 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="1" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
@@ -1136,18 +1202,14 @@
       <c r="F17" s="1" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>房前 輝</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>失点</t>
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="1" t="inlineStr"/>
       <c r="E18" s="1" t="inlineStr"/>
@@ -1155,188 +1217,855 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>4</v>
-      </c>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
       <c r="D19" s="1" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr"/>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>寺田 真歩人</t>
+          <t>2回表 1点目</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>失点</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>徳竹 智大</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>原尻 颯太</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>自責</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>志賀 亮佑</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>小林 宅登</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>非自責</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>新村 勇翔</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>菊田 翔友</t>
+          <t>3回裏 3点目</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>失点</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
+          <t>3回裏 3点目</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>橋本 涼</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>3</v>
-      </c>
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr"/>
       <c r="D25" s="1" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr"/>
       <c r="F25" s="1" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="1" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr"/>
       <c r="F27" s="1" t="inlineStr"/>
     </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EasyScoreJudge Phoenix Daily Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>02_鳥取大学－下関市立大：EasyScore補正票</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>試合名</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>02_鳥取大学－下関市立大</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>確認状態</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>□未確認  □補正済  □再確認</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>総得点</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>自責候補</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>本日の補正</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>補正作業</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>走者/内容</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2回表 2点目</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>坂本 就希斗</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>田村 亮</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>5回表 1点目</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>勝田 将真</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>7回表 1点目</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>横山 颯真</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>7回表 2点目</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>捕逸生還</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>清水 将太郎</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>7回表 3点目</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>岩見 拓馬</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr"/>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>松田 弘貴</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>山下 佳輝</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>宋 和陽</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr"/>
+      <c r="D26" s="1" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>得点詳細</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>理由</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>走者</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>確認</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>松田 弘貴</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>岩見 拓馬</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2回表 1点目</t>
+          <t>2回表 2点目</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>2回表 1点目</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>2回表 2点目</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>伊敷 聖羅</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>幸野 祐介</t>
+          <t>坂本 就希斗</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -1348,27 +2077,27 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2回表 2点目</t>
+          <t>3回裏 1点目</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>2回表 2点目</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>伊敷 聖羅</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>西原 凜</t>
+          <t>田村 亮</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -1380,12 +2109,12 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>4回表 1点目</t>
+          <t>5回表 1点目</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>4回表 1点目</t>
+          <t>5回表 1点目</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1395,12 +2124,12 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>西原 凜</t>
+          <t>勝田 将真</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -1412,27 +2141,27 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>5回裏 1点目</t>
+          <t>7回表 1点目</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>5回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>7回表 1点目</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>房前 輝</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>岡田 子騰</t>
+          <t>横山 颯真</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -1444,27 +2173,27 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>5回裏 2点目</t>
+          <t>7回表 2点目</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>5回裏 2点目</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>7回表 2点目</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>房前 輝</t>
+          <t>捕逸生還</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>窪田 翔太</t>
+          <t>清水 将太郎</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -1476,27 +2205,27 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>5回裏 3点目</t>
+          <t>7回表 3点目</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>5回裏 3点目</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>7回表 3点目</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>房前 輝</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>椋本 一冴</t>
+          <t>岩見 拓馬</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -1506,280 +2235,56 @@
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>5回裏 4点目</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>5回裏 4点目</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>失策生還</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>杉 ケニス 千音々</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr"/>
+      <c r="C35" s="1" t="inlineStr"/>
+      <c r="D35" s="1" t="inlineStr"/>
+      <c r="E35" s="1" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>5回裏 5点目</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>5回裏 5点目</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>房前 輝</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>岡村 雄斗</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>5回裏 6点目</t>
-        </is>
-      </c>
+      <c r="A37" s="1" t="inlineStr"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>5回裏 6点目</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>Virtual生還不能</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>太田 直哉</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>6回表 1点目</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>6回表 1点目</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>菊田 翔友</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>川原 雄大</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>6回表 2点目</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>6回表 2点目</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>菊田 翔友</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>笠谷 俊介</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>6回表 3点目</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>6回表 3点目</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>菊田 翔友</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>本田 凪汐</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>6回裏 1点目</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>6回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>失策出塁</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>窪田 翔太</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Review詳細</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>レベル</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>信頼度</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
+      <c r="C37" s="1" t="inlineStr"/>
+      <c r="D37" s="1" t="inlineStr"/>
+      <c r="E37" s="1" t="inlineStr"/>
+      <c r="F37" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Neo_Phoenix/reports/daily_check.xlsx
+++ b/Neo_Phoenix/reports/daily_check.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="DaySummary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Game1_01_山口大学－広島大学" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Game2_02_鳥取大学－下関市立大" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Game1_01_敦賀気比－横手" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game2_02_履正社－享栄" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Game3_03_松商学園－三重" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'DaySummary'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_山口大学－広島大学'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Game2_02_鳥取大学－下関市立大'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_敦賀気比－横手'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Game2_02_履正社－享栄'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Game3_03_松商学園－三重'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -546,7 +548,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22 10:36:41</t>
+          <t>2026-08-12 13:03:44</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -590,7 +592,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2試合</t>
+          <t>3試合</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -600,7 +602,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8件</t>
+          <t>9件</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -665,17 +667,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>□ 01_山口大学－広島大学</t>
+          <t>□ 01_敦賀気比－横手</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>3回裏 2点目　非自責</t>
+          <t>3回表 1点目　非自責</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -689,17 +691,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>□ 01_山口大学－広島大学</t>
+          <t>□ 01_敦賀気比－横手</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>3回裏 3点目　非自責</t>
+          <t>3回表 2点目　非自責</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Virtual3アウト</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -713,17 +715,17 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>□ 02_鳥取大学－下関市立大</t>
+          <t>□ 01_敦賀気比－横手</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2回表 2点目　非自責</t>
+          <t>3回表 3点目　非自責</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -737,17 +739,17 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>□ 02_鳥取大学－下関市立大</t>
+          <t>□ 01_敦賀気比－横手</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>3回裏 1点目　非自責</t>
+          <t>3回表 4点目　非自責</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -761,12 +763,12 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>□ 02_鳥取大学－下関市立大</t>
+          <t>□ 01_敦賀気比－横手</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>5回表 1点目　非自責</t>
+          <t>3回表 5点目　非自責</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -785,17 +787,17 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>□ 02_鳥取大学－下関市立大</t>
+          <t>□ 02_履正社－享栄</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>7回表 1点目　非自責</t>
+          <t>1回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -809,17 +811,17 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>□ 02_鳥取大学－下関市立大</t>
+          <t>□ 02_履正社－享栄</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>7回表 2点目　非自責</t>
+          <t>9回表 1点目　非自責</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>捕逸生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -833,17 +835,17 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>□ 02_鳥取大学－下関市立大</t>
+          <t>□ 02_履正社－享栄</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>7回表 3点目　非自責</t>
+          <t>9回表 2点目　非自責</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -853,6 +855,30 @@
       </c>
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_松商学園－三重</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>3回裏 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -870,7 +896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -896,7 +922,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>01_山口大学－広島大学：EasyScore補正票</t>
+          <t>01_敦賀気比－横手：EasyScore補正票</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -921,7 +947,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>01_山口大学－広島大学</t>
+          <t>01_敦賀気比－横手</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -944,7 +970,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -952,7 +978,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -960,7 +986,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1039,7 +1065,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>3回裏 2点目</t>
+          <t>3回表 1点目</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1049,12 +1075,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>新村 勇翔</t>
+          <t>鵜飼 新馬</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -1071,7 +1097,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3回裏 3点目</t>
+          <t>3回表 2点目</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1081,98 +1107,148 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>長谷川 陽竜</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>3回表 3点目</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>後藤 駿平</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>3回表 4点目</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
           <t>Virtual3アウト</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>橋本 涼</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="1" t="inlineStr"/>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" s="1" t="inlineStr"/>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>投手サマリー</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>村雲 脩吾</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>徳竹 智大</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>失点</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="inlineStr"/>
-      <c r="E13" s="1" t="inlineStr"/>
-      <c r="F13" s="1" t="inlineStr"/>
+          <t>3回表 5点目</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>川原 成翔</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="1" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr"/>
       <c r="D14" s="1" t="inlineStr"/>
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="1" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1" t="inlineStr"/>
-      <c r="E15" s="1" t="inlineStr"/>
-      <c r="F15" s="1" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>志賀 亮佑</t>
+          <t>佐藤 宙斗</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -1181,7 +1257,7 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="inlineStr"/>
       <c r="E16" s="1" t="inlineStr"/>
@@ -1195,7 +1271,7 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="1" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr"/>
@@ -1209,7 +1285,7 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="1" t="inlineStr"/>
       <c r="E18" s="1" t="inlineStr"/>
@@ -1258,12 +1334,12 @@
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2回表 1点目</t>
+          <t>1回表 1点目</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>2回表 1点目</t>
+          <t>1回表 1点目</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1273,12 +1349,12 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>徳竹 智大</t>
+          <t>佐藤 宙斗</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>原尻 颯太</t>
+          <t>伊藤 綸一</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -1290,27 +1366,27 @@
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>3回裏 1点目</t>
+          <t>3回表 1点目</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>3回表 1点目</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>志賀 亮佑</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>小林 宅登</t>
+          <t>鵜飼 新馬</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -1322,12 +1398,12 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>3回裏 2点目</t>
+          <t>3回表 2点目</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3回裏 2点目</t>
+          <t>3回表 2点目</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1337,12 +1413,12 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>新村 勇翔</t>
+          <t>長谷川 陽竜</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -1354,12 +1430,12 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>3回裏 3点目</t>
+          <t>3回表 3点目</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3回裏 3点目</t>
+          <t>3回表 3点目</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1369,71 +1445,263 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>後藤 駿平</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>3回表 4点目</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>3回表 4点目</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
           <t>Virtual3アウト</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>橋本 涼</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>村雲 脩吾</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>3回表 5点目</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>3回表 5点目</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>川原 成翔</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 宙斗</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>長谷川 陽竜</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>5回表 1点目</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>5回表 1点目</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 宙斗</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>村雲 脩吾</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>5回表 2点目</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>5回表 2点目</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 宙斗</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>川原 成翔</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8回表 1点目</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>8回表 1点目</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 宙斗</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>伊藤 綸一</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="1" t="inlineStr"/>
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr"/>
+      <c r="D31" s="1" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr"/>
+      <c r="F31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Review詳細</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>場所</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>信頼度</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="1" t="inlineStr"/>
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr"/>
+      <c r="D33" s="1" t="inlineStr"/>
+      <c r="E33" s="1" t="inlineStr"/>
+      <c r="F33" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1451,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1745,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02_鳥取大学－下関市立大：EasyScore補正票</t>
+          <t>02_履正社－享栄：EasyScore補正票</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -1502,7 +1770,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>02_鳥取大学－下関市立大</t>
+          <t>02_履正社－享栄</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -1525,7 +1793,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -1533,7 +1801,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -1541,7 +1809,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1620,7 +1888,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>2回表 2点目</t>
+          <t>1回裏 1点目</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1630,12 +1898,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>坂本 就希斗</t>
+          <t>早川 来輝</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -1652,7 +1920,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3回裏 1点目</t>
+          <t>9回表 1点目</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1662,12 +1930,12 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>田村 亮</t>
+          <t>城間 煌陽</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -1684,7 +1952,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>5回表 1点目</t>
+          <t>9回表 2点目</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1699,7 +1967,7 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>勝田 将真</t>
+          <t>岩本 倫之介</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -1709,133 +1977,83 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>7回表 1点目</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>失策生還</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>横山 颯真</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="inlineStr"/>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr"/>
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>7回表 2点目</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>捕逸生還</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>清水 将太郎</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>木村 颯</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>7回表 3点目</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Virtual生還不能</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>岩見 拓馬</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="1" t="inlineStr"/>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="D15" s="1" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>投手サマリー</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>松田 弘貴</t>
+          <t>近藤 優</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
@@ -1844,7 +2062,7 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr"/>
@@ -1858,7 +2076,7 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="1" t="inlineStr"/>
       <c r="E18" s="1" t="inlineStr"/>
@@ -1872,7 +2090,7 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr"/>
@@ -1881,7 +2099,7 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>山下 佳輝</t>
+          <t>上江滝 拓未</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
@@ -1890,7 +2108,7 @@
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="inlineStr"/>
       <c r="E20" s="1" t="inlineStr"/>
@@ -1904,7 +2122,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="inlineStr"/>
       <c r="E21" s="1" t="inlineStr"/>
@@ -1918,7 +2136,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="inlineStr"/>
       <c r="E22" s="1" t="inlineStr"/>
@@ -1927,7 +2145,7 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>宋 和陽</t>
+          <t>坂本 亮太</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
@@ -1936,7 +2154,7 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="1" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr"/>
@@ -1964,7 +2182,7 @@
         </is>
       </c>
       <c r="C25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="inlineStr"/>
       <c r="E25" s="1" t="inlineStr"/>
@@ -2013,27 +2231,27 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2回表 1点目</t>
+          <t>1回裏 1点目</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>2回表 1点目</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>松田 弘貴</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>岩見 拓馬</t>
+          <t>早川 来輝</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -2045,27 +2263,27 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2回表 2点目</t>
+          <t>2回表 1点目</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>2回表 2点目</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>近藤 優</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>坂本 就希斗</t>
+          <t>辻󠄀 竜乃介</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -2077,27 +2295,27 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>3回裏 1点目</t>
+          <t>4回表 1点目</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>近藤 優</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>田村 亮</t>
+          <t>北西 華一</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -2109,27 +2327,27 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>5回表 1点目</t>
+          <t>8回表 1点目</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>5回表 1点目</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
+          <t>8回表 1点目</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Virtual3アウト</t>
+          <t>上江滝 拓未</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>勝田 将真</t>
+          <t>竿谷 凜斗</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -2141,27 +2359,27 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>7回表 1点目</t>
+          <t>8回表 2点目</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>7回表 1点目</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
+          <t>8回表 2点目</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>上江滝 拓未</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>横山 颯真</t>
+          <t>小杉 悠人</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -2173,12 +2391,12 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>7回表 2点目</t>
+          <t>9回表 1点目</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>7回表 2点目</t>
+          <t>9回表 1点目</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2188,12 +2406,12 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>捕逸生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>清水 将太郎</t>
+          <t>城間 煌陽</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -2205,12 +2423,12 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>7回表 3点目</t>
+          <t>9回表 2点目</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>7回表 3点目</t>
+          <t>9回表 2点目</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2220,12 +2438,12 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>岩見 拓馬</t>
+          <t>岩本 倫之介</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -2235,56 +2453,857 @@
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>木村 颯</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>藤井 陽斗</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Review詳細</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>場所</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>信頼度</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr">
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
+      <c r="C38" s="1" t="inlineStr"/>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EasyScoreJudge Phoenix Daily Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>03_松商学園－三重：EasyScore補正票</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>試合名</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>03_松商学園－三重</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>確認状態</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>□未確認  □補正済  □再確認</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>総得点</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>自責候補</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>本日の補正</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>補正作業</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>走者/内容</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>前野 元佑</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="inlineStr"/>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr"/>
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr"/>
+      <c r="F10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>竹内 篤希</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 大牙</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>船橋 昊</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>吉井 海翔</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr"/>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>竹内 篤希</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>前野 元佑</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>竹内 篤希</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>秋山 隼人</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>前野 元佑</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 大牙</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>水野 央清</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 大牙</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>前野 元佑</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>8回表 1点目</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>8回表 1点目</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>船橋 昊</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>山口 史晃</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>9回表 1点目</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>9回表 1点目</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>吉井 海翔</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>平沢 陸</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>9回表 2点目</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>9回表 2点目</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>吉井 海翔</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>花沢 玲希</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
